--- a/docs/kostenuebersicht-finance.xlsx
+++ b/docs/kostenuebersicht-finance.xlsx
@@ -25,15 +25,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; $&quot;;\(#,##0.00&quot; $)&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;;\(#,##0.00&quot; €)&quot;"/>
     <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="mmm\ yyyy"/>
+    <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -143,6 +144,16 @@
       <i val="1"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
     </font>
   </fonts>
   <fills count="7">
@@ -274,7 +285,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="225">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -917,6 +928,21 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1840,10 +1866,21 @@
       <c r="H19" s="122" t="n"/>
       <c r="I19" s="122" t="n"/>
     </row>
+    <row r="20">
+      <c r="A20" s="216" t="inlineStr">
+        <is>
+          <t>Summe gesamt in EUR (USD-Positionen zum BMF-Kurs August 2026)</t>
+        </is>
+      </c>
+      <c r="D20" s="217">
+        <f>D19+D18/Rechnungsjournal!$B$42</f>
+        <v/>
+      </c>
+    </row>
     <row r="21" ht="15" customHeight="1" s="108">
       <c r="A21" s="110" t="inlineStr">
         <is>
-          <t>Hinweis: USD- und EUR-Positionen werden bewusst getrennt summiert, um keinen falschen Umrechnungskurs vorzutäuschen. Beleg-Details je Rechnung (Rechnungsnummer, Netto/USt/Brutto, Beleg-Datei) stehen im Blatt 'Rechnungsjournal'.</t>
+          <t>Hinweis: USD- und EUR-Positionen werden weiterhin getrennt summiert, weil die Belege in unterschiedlichen Währungen vorliegen. Die Gesamtsumme in EUR rechnet die USD-Positionen mit dem amtlichen BMF-Umsatzsteuer-Umrechnungskurs des jeweils letzten Monats um (§ 16 Abs. 6 UStG) — die Kurse stehen im Blatt 'Rechnungsjournal' unter der Journaltabelle. Beleg-Details je Rechnung (Rechnungsnummer, Netto/USt/Brutto, Beleg-Datei) stehen ebenfalls im Blatt 'Rechnungsjournal'.</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1961,7 @@
     <row r="10" ht="15" customHeight="1" s="108">
       <c r="A10" s="212" t="inlineStr">
         <is>
-          <t>Gelbe Füllung = noch offen / noch kein Wert eingetragen (z. B. EUR-Umrechnung, fehlender Monat).</t>
+          <t>Gelbe Füllung = noch offen / noch kein Wert eingetragen (z. B. fehlender Monat, noch nicht aufgefundener Beleg).</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2136,7 @@
     <row r="40" ht="26.85" customHeight="1" s="108">
       <c r="A40" s="214" t="inlineStr">
         <is>
-          <t>• ERLEDIGT 17.09.2026 (Head of Finance): Supabase-Reverse-Charge-Rechnungen bei § 19 UStG — Sandy schuldet die 19 % deutsche USt selbst (§ 13b Abs. 2 Nr. 1 i. V. m. Abs. 5 UStG); § 19 schützt nur die eigenen Verkäufe, ein Vorsteuerabzug besteht nicht (§ 19 Abs. 1 i. V. m. § 15 UStG). Es sind also echte Kosten. Bisher aufgelaufen: 34,79 USD auf 183,10 USD Netto (Belege 2026-003/006/008/016), laufend rund 10 USD je Monat. Voranmeldung für die betroffenen Zeiträume nach § 18 Abs. 4a UStG. Nur noch für den Steuerberater: ab wann die Unternehmereigenschaft bestand (Vorbereitungshandlungen ab Mai 2026) und wie das über den Fragebogen zur steuerlichen Erfassung nach der Gewerbeanmeldung (KW 41) nachgeholt wird. Herleitung und Quellen im Eintrag vom 17.09.2026 in docs/chief-of-staff-finance-todos.md.</t>
+          <t>• ERLEDIGT 17.09.2026 (Head of Finance): Supabase-Reverse-Charge-Rechnungen bei § 19 UStG — Sandy schuldet die 19 % deutsche USt selbst (§ 13b Abs. 2 Nr. 1 i. V. m. Abs. 5 UStG); § 19 schützt nur die eigenen Verkäufe, ein Vorsteuerabzug besteht nicht (§ 19 Abs. 1 i. V. m. § 15 UStG). Es sind also echte Kosten. Bisher aufgelaufen: 34,79 USD auf 183,10 USD Netto (Belege 2026-003/006/008/016), laufend rund 10 USD je Monat. Voranmeldung für die betroffenen Zeiträume nach § 18 Abs. 4a UStG. Nur noch für den Steuerberater: ab wann die Unternehmereigenschaft bestand (Vorbereitungshandlungen ab Mai 2026) und wie das über den Fragebogen zur steuerlichen Erfassung nach der Gewerbeanmeldung (KW 41) nachgeholt wird. Herleitung und Quellen im Eintrag vom 17.09.2026 in docs/chief-of-staff-finance-todos.md. Ergänzt 17.09.2026: in Euro sind das 30,17 € Umsatzsteuer auf 158,79 € Netto (Umrechnung zu den amtlichen BMF-Monatskursen, siehe Kurstabelle im Blatt Rechnungsjournal); laufend rund 8,80 € im Monat.</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2164,7 @@
     <row r="44" ht="26.85" customHeight="1" s="108">
       <c r="A44" s="214" t="inlineStr">
         <is>
-          <t>• EUR-Umrechnung der USD-Rechnungen (Spalte 'Betrag EUR' im Journal) ist bewusst noch offen — welchen Umrechnungskurs soll ich verwenden, sobald ein Steuerberater feststeht?</t>
+          <t>• ERLEDIGT 17.09.2026 (Head of Finance): EUR-Umrechnung der USD-Rechnungen. Es braucht dafür keine Entscheidung des Steuerberaters — § 16 Abs. 6 UStG schreibt die vom BMF monatlich veröffentlichten Durchschnittskurse zwingend vor. Maßgeblich ist der Monat des Rechnungsdatums. Kurse 2026 (USD je 1 EUR): Mai 1,1673 · Juni 1,1518 · Juli 1,1417 · August 1,1593 (BMF-Schreiben vom 01.09.2026, Gz. III C 3 - S 7329/00014/008/112). Spalte 'Betrag EUR' im Journal ist gefüllt und rechnet über die Kurstabelle unter der Journaltabelle; ein neuer Monat wird dort eingetragen, nicht in jede Zeile. Für die Einnahmenüberschussrechnung wird derselbe Kurs verwendet, damit nur eine Methode im Haus ist.</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="107" min="1" max="1"/>
@@ -2439,7 +2476,10 @@
           <t>USt. (19%) direkt von Vercel ausgewiesen (EU VAT EU056329113), kein Reverse Charge.</t>
         </is>
       </c>
-      <c r="P6" s="129" t="n"/>
+      <c r="P6" s="127">
+        <f>M6/$B$39</f>
+        <v/>
+      </c>
       <c r="Q6" s="112" t="inlineStr">
         <is>
           <t>Kreditkarte Visa •••3991</t>
@@ -2522,7 +2562,10 @@
           <t>Reverse Charge — Supabase weist keine USt aus. Sandy startet als Kleinunternehmerin nach §19 UStG (bestätigt 19.08.2026), Gewerbe aber noch nicht angemeldet. Nach Kleinunternehmerregelung i. d. R. keine Vorsteuer ziehbar, aber die USt-Pflicht auf reverse-charge-Leistungen aus dem Ausland (§13b UStG) kann trotzdem bestehen bleiben — das ist keine verbindliche Auskunft von mir, bitte mit Steuerberater final klären, sobald einer feststeht.</t>
         </is>
       </c>
-      <c r="P7" s="129" t="n"/>
+      <c r="P7" s="127">
+        <f>M7/$B$39</f>
+        <v/>
+      </c>
       <c r="Q7" s="112" t="inlineStr">
         <is>
           <t>unbekannt</t>
@@ -2603,7 +2646,10 @@
           <t>USt. (19%) direkt von OpenAI ausgewiesen (EU OSS VAT EU372041333), kein Reverse Charge.</t>
         </is>
       </c>
-      <c r="P8" s="129" t="n"/>
+      <c r="P8" s="127">
+        <f>M8/$B$40</f>
+        <v/>
+      </c>
       <c r="Q8" s="112" t="inlineStr">
         <is>
           <t>unbekannt</t>
@@ -2684,7 +2730,10 @@
           <t>USt. (19%) direkt von Vercel ausgewiesen (EU VAT EU056329113), kein Reverse Charge.</t>
         </is>
       </c>
-      <c r="P9" s="129" t="n"/>
+      <c r="P9" s="127">
+        <f>M9/$B$40</f>
+        <v/>
+      </c>
       <c r="Q9" s="112" t="inlineStr">
         <is>
           <t>Kreditkarte Visa •••3991</t>
@@ -2767,7 +2816,10 @@
           <t>Reverse Charge — Supabase weist keine USt aus. Sandy startet als Kleinunternehmerin nach §19 UStG (bestätigt 19.08.2026), Gewerbe aber noch nicht angemeldet. Nach Kleinunternehmerregelung i. d. R. keine Vorsteuer ziehbar, aber die USt-Pflicht auf reverse-charge-Leistungen aus dem Ausland (§13b UStG) kann trotzdem bestehen bleiben — das ist keine verbindliche Auskunft von mir, bitte mit Steuerberater final klären, sobald einer feststeht.</t>
         </is>
       </c>
-      <c r="P10" s="129" t="n"/>
+      <c r="P10" s="127">
+        <f>M10/$B$40</f>
+        <v/>
+      </c>
       <c r="Q10" s="112" t="inlineStr">
         <is>
           <t>unbekannt</t>
@@ -2848,7 +2900,10 @@
           <t>USt. (19%) direkt von Vercel ausgewiesen (EU VAT EU056329113), kein Reverse Charge.</t>
         </is>
       </c>
-      <c r="P11" s="129" t="n"/>
+      <c r="P11" s="127">
+        <f>M11/$B$41</f>
+        <v/>
+      </c>
       <c r="Q11" s="112" t="inlineStr">
         <is>
           <t>Kreditkarte Visa •••3991</t>
@@ -2931,7 +2986,10 @@
           <t>Reverse Charge — Supabase weist keine USt aus. Sandy startet als Kleinunternehmerin nach §19 UStG (bestätigt 19.08.2026), Gewerbe aber noch nicht angemeldet. Nach Kleinunternehmerregelung i. d. R. keine Vorsteuer ziehbar, aber die USt-Pflicht auf reverse-charge-Leistungen aus dem Ausland (§13b UStG) kann trotzdem bestehen bleiben — das ist keine verbindliche Auskunft von mir, bitte mit Steuerberater final klären, sobald einer feststeht.</t>
         </is>
       </c>
-      <c r="P12" s="129" t="n"/>
+      <c r="P12" s="127">
+        <f>M12/$B$41</f>
+        <v/>
+      </c>
       <c r="Q12" s="112" t="inlineStr">
         <is>
           <t>unbekannt</t>
@@ -3096,7 +3154,10 @@
           <t>USt. (19%) direkt von Anthropic ausgewiesen (EU VAT IE4276970QH), kein Reverse Charge.</t>
         </is>
       </c>
-      <c r="P14" s="129" t="n"/>
+      <c r="P14" s="127">
+        <f>M14/$B$42</f>
+        <v/>
+      </c>
       <c r="Q14" s="112" t="inlineStr">
         <is>
           <t>unbekannt (Online-Zahlung)</t>
@@ -3513,7 +3574,10 @@
           <t>USt. (19%) direkt von Vercel ausgewiesen (EU VAT EU056329113), kein Reverse Charge.</t>
         </is>
       </c>
-      <c r="P19" s="129" t="n"/>
+      <c r="P19" s="127">
+        <f>M19/$B$42</f>
+        <v/>
+      </c>
       <c r="Q19" s="112" t="inlineStr">
         <is>
           <t>Kreditkarte Visa •••3991</t>
@@ -3596,7 +3660,10 @@
           <t>Reverse Charge — Supabase weist keine USt aus. Sandy startet als Kleinunternehmerin nach §19 UStG (bestätigt 19.08.2026), Gewerbe aber noch nicht angemeldet. Nach Kleinunternehmerregelung i. d. R. keine Vorsteuer ziehbar, aber die USt-Pflicht auf reverse-charge-Leistungen aus dem Ausland (§13b UStG) kann trotzdem bestehen bleiben — das ist keine verbindliche Auskunft von mir, bitte mit Steuerberater final klären, sobald einer feststeht.</t>
         </is>
       </c>
-      <c r="P20" s="129" t="n"/>
+      <c r="P20" s="127">
+        <f>M20/$B$42</f>
+        <v/>
+      </c>
       <c r="Q20" s="112" t="inlineStr">
         <is>
           <t>unbekannt</t>
@@ -3740,7 +3807,7 @@
       <c r="S23" s="130" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="108">
-      <c r="A24" s="130" t="n"/>
+      <c r="A24" s="218" t="n"/>
       <c r="B24" s="130" t="n"/>
       <c r="C24" s="130" t="n"/>
       <c r="D24" s="130" t="n"/>
@@ -3761,8 +3828,8 @@
       <c r="S24" s="130" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="108">
-      <c r="A25" s="130" t="n"/>
-      <c r="B25" s="130" t="n"/>
+      <c r="A25" s="219" t="n"/>
+      <c r="B25" s="219" t="n"/>
       <c r="C25" s="130" t="n"/>
       <c r="D25" s="130" t="n"/>
       <c r="E25" s="130" t="n"/>
@@ -3783,7 +3850,7 @@
     </row>
     <row r="26" ht="15" customHeight="1" s="108">
       <c r="A26" s="130" t="n"/>
-      <c r="B26" s="130" t="n"/>
+      <c r="B26" s="220" t="n"/>
       <c r="C26" s="130" t="n"/>
       <c r="D26" s="130" t="n"/>
       <c r="E26" s="130" t="n"/>
@@ -3804,7 +3871,7 @@
     </row>
     <row r="27" ht="15" customHeight="1" s="108">
       <c r="A27" s="130" t="n"/>
-      <c r="B27" s="130" t="n"/>
+      <c r="B27" s="220" t="n"/>
       <c r="C27" s="130" t="n"/>
       <c r="D27" s="130" t="n"/>
       <c r="E27" s="130" t="n"/>
@@ -3825,7 +3892,7 @@
     </row>
     <row r="28" ht="15" customHeight="1" s="108">
       <c r="A28" s="130" t="n"/>
-      <c r="B28" s="130" t="n"/>
+      <c r="B28" s="220" t="n"/>
       <c r="C28" s="130" t="n"/>
       <c r="D28" s="130" t="n"/>
       <c r="E28" s="130" t="n"/>
@@ -3846,7 +3913,7 @@
     </row>
     <row r="29" ht="15" customHeight="1" s="108">
       <c r="A29" s="130" t="n"/>
-      <c r="B29" s="130" t="n"/>
+      <c r="B29" s="220" t="n"/>
       <c r="C29" s="130" t="n"/>
       <c r="D29" s="130" t="n"/>
       <c r="E29" s="130" t="n"/>
@@ -3887,7 +3954,7 @@
       <c r="S30" s="130" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="108">
-      <c r="A31" s="130" t="n"/>
+      <c r="A31" s="221" t="n"/>
       <c r="B31" s="130" t="n"/>
       <c r="C31" s="130" t="n"/>
       <c r="D31" s="130" t="n"/>
@@ -3969,6 +4036,72 @@
       <c r="Q34" s="130" t="n"/>
       <c r="R34" s="130" t="n"/>
       <c r="S34" s="130" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="222" t="inlineStr">
+        <is>
+          <t>Umrechnung USD → EUR — BMF-Umsatzsteuer-Umrechnungskurse (§ 16 Abs. 6 UStG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="223" t="inlineStr">
+        <is>
+          <t>Monat 2026</t>
+        </is>
+      </c>
+      <c r="B38" s="223" t="inlineStr">
+        <is>
+          <t>Kurs (USD je 1 EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="107" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B39" s="224" t="n">
+        <v>1.1673</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="107" t="inlineStr">
+        <is>
+          <t>Juni</t>
+        </is>
+      </c>
+      <c r="B40" s="224" t="n">
+        <v>1.1518</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="107" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="B41" s="224" t="n">
+        <v>1.1417</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="107" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="B42" s="224" t="n">
+        <v>1.1593</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="107" t="inlineStr">
+        <is>
+          <t>Maßgeblich ist der Monat des Rechnungsdatums (bei Supabase zugleich der Monat, in dem die Dauerleistung endet und die Steuer nach § 13b UStG entsteht). Quelle: BMF-Schreiben vom 01.09.2026, Gz. III C 3 - S 7329/00014/008/112, monatlich fortgeschriebene Übersicht 2026. Neuen Monat hier ergänzen — Spalte P rechnet dann von selbst. Für EUR-Belege verweist Spalte P unverändert auf den Bruttobetrag.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5832,7 +5965,7 @@
       </c>
       <c r="D20" s="163" t="inlineStr">
         <is>
-          <t>exchange-rates.org: 01.09.2026 = 0,8626, 02.09.2026 = 0,8631, YTD-Ø 0,8603. Supabase, Vercel, OpenAI und Anthropic rechnen in US-Dollar — der Kurs steht deshalb sichtbar hier.</t>
+          <t>exchange-rates.org: 01.09.2026 = 0,8626, 02.09.2026 = 0,8631, YTD-Ø 0,8603. Supabase, Vercel, OpenAI und Anthropic rechnen in US-Dollar — der Kurs steht deshalb sichtbar hier. Nachgeprüft 17.09.2026 (Head of Finance): Der amtliche BMF-Umsatzsteuer-Umrechnungskurs für August 2026 beträgt 1,1593 USD je EUR = 0,8626 EUR je USD und bestätigt diesen Planwert (Abweichung 0,3 %, rund 0,33 € im Monat). Bewusst zwei verschiedene Kurse mit zwei verschiedenen Aufgaben: hier ein Planungskurs für künftige Monate, im Blatt Rechnungsjournal der amtliche Monatskurs für die Buchung bereits vorliegender Belege (§ 16 Abs. 6 UStG). Bitte nicht angleichen.</t>
         </is>
       </c>
       <c r="E20" s="160" t="n"/>

--- a/docs/kostenuebersicht-finance.xlsx
+++ b/docs/kostenuebersicht-finance.xlsx
@@ -1820,14 +1820,42 @@
       <c r="I15" s="112" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="108">
-      <c r="A16" s="118" t="n"/>
-      <c r="B16" s="112" t="n"/>
-      <c r="C16" s="112" t="n"/>
-      <c r="D16" s="120" t="n"/>
-      <c r="E16" s="112" t="n"/>
-      <c r="F16" s="112" t="n"/>
-      <c r="G16" s="112" t="n"/>
-      <c r="H16" s="112" t="n"/>
+      <c r="A16" s="112" t="inlineStr">
+        <is>
+          <t>DIN Media — VOB Gesamtausgabe 2019 (E-Book)</t>
+        </is>
+      </c>
+      <c r="B16" s="112" t="inlineStr">
+        <is>
+          <t>Fachliteratur — einmalig</t>
+        </is>
+      </c>
+      <c r="C16" s="112" t="inlineStr">
+        <is>
+          <t>EUR einmalig</t>
+        </is>
+      </c>
+      <c r="D16" s="119" t="n"/>
+      <c r="E16" s="112" t="inlineStr">
+        <is>
+          <t>einmalig, 54,00 € brutto am 04.09.2026 (Beleg 2026-018)</t>
+        </is>
+      </c>
+      <c r="F16" s="112" t="inlineStr">
+        <is>
+          <t>kein Vertrag, Einmalkauf</t>
+        </is>
+      </c>
+      <c r="G16" s="112" t="inlineStr">
+        <is>
+          <t>USt. 7 % ermaessigt (E-Book), von DIN Media ausgewiesen</t>
+        </is>
+      </c>
+      <c r="H16" s="112" t="inlineStr">
+        <is>
+          <t>bestätigt — kein laufender Posten, steht deshalb ohne Monatsbetrag und faellt nicht in die Monatssummen</t>
+        </is>
+      </c>
       <c r="I16" s="112" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="108">
@@ -2175,7 +2203,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="39.55" customHeight="1" s="108"/>
+    <row r="46" ht="39.55" customHeight="1" s="108">
+      <c r="A46" s="214" t="inlineStr">
+        <is>
+          <t>• NEU 17.09.2026 (Head of Finance): Beleg 2026-018, DIN Media GmbH, 54,00 € brutto (50,47 € netto + 3,53 € USt zu 7 %) — die erste echte E-Rechnung im Eingang (ZUGFeRD/Factur-X EXTENDED). Einmalige Anschaffung, deshalb NUR im Rechnungsjournal und NICHT in Kostenuebersicht-Monatsbetrag oder Monatsverlauf: beide fuehren ausschliesslich laufende Kosten. Wer die Gesamtausgaben 2026 braucht, summiert das Rechnungsjournal, nicht die Kostenuebersicht. Unter Regelbesteuerung (Entscheidung F-006 = B) sind die 3,53 € Vorsteuer.</t>
+        </is>
+      </c>
+    </row>
     <row r="47">
       <c r="A47" s="215" t="inlineStr">
         <is>
@@ -2196,7 +2230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:T44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="107" min="1" max="1"/>
@@ -2327,6 +2361,11 @@
           <t>Auffälligkeit / Notiz</t>
         </is>
       </c>
+      <c r="T4" s="111" t="inlineStr">
+        <is>
+          <t>Vorsteuer EUR (erst ab Regelbesteuerung, F-006 = B)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="64.90000000000001" customHeight="1" s="108">
       <c r="A5" s="112" t="inlineStr">
@@ -2411,6 +2450,10 @@
           <t>Abo verlängert sich automatisch monatlich. Rechnungsadresse weicht von den übrigen Belegen ab (Krampasplatz 4b statt Wielandstraße 11) — bitte klären, welche Adresse aktuell/richtig ist.</t>
         </is>
       </c>
+      <c r="T5" s="128">
+        <f>ROUND(L5,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="52.2" customHeight="1" s="108">
       <c r="A6" s="112" t="inlineStr">
@@ -2495,6 +2538,10 @@
           <t>Zahlungsart nachträglich ergänzt (Update 2026-09-02) anhand Zahlungsbeleg Receipt-2392-5328.pdf.</t>
         </is>
       </c>
+      <c r="T6" s="128">
+        <f>ROUND(L6/$B$39,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="179.1" customHeight="1" s="108">
       <c r="A7" s="112" t="inlineStr">
@@ -2581,6 +2628,11 @@
           <t>Nur Pro-Plan-Grundgebühr, keine Nutzungsgebühren in diesem Monat.</t>
         </is>
       </c>
+      <c r="T7" s="128" t="inlineStr">
+        <is>
+          <t>0,00 (durchlaufend)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="90.25" customHeight="1" s="108">
       <c r="A8" s="112" t="inlineStr">
@@ -2665,6 +2717,10 @@
           <t>Geklärt (19.08.2026): Konto gehört Sandy, 'Hugo' ist ein historischer Nutzername/E-Mail-Alias bei OpenAI, der sich im Nachhinein nicht mehr auf 'Sandra Holm' ändern lässt. Kein falscher Account — nur zur Info für den Steuerberater vermerkt, falls Name/E-Mail auf dem Beleg auffallen.</t>
         </is>
       </c>
+      <c r="T8" s="128">
+        <f>ROUND(L8/$B$40,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="64.90000000000001" customHeight="1" s="108">
       <c r="A9" s="112" t="inlineStr">
@@ -2749,6 +2805,10 @@
           <t>Zusätzliche Position 'Observability Plus' mit $0,00 seit diesem Monat. Zahlungsart nachträglich ergänzt (Update 2026-09-02) anhand Zahlungsbeleg Receipt-2268-5813.pdf.</t>
         </is>
       </c>
+      <c r="T9" s="128">
+        <f>ROUND(L9/$B$40,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="179.1" customHeight="1" s="108">
       <c r="A10" s="112" t="inlineStr">
@@ -2835,6 +2895,11 @@
           <t>Erstmals nennenswerte Nutzungsgebühren (Compute Hours) zusätzlich zur Pro-Plan-Grundgebühr. Zahlungsbeleg (Receipt-MVGOOM-00005.pdf) nachträglich ergänzt (Update 2026-09-02), keine neue Zeile — identischer Betrag/Zeitraum wie diese Rechnung.</t>
         </is>
       </c>
+      <c r="T10" s="128" t="inlineStr">
+        <is>
+          <t>0,00 (durchlaufend)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="52.2" customHeight="1" s="108">
       <c r="A11" s="112" t="inlineStr">
@@ -2919,6 +2984,10 @@
           <t>Zahlungsart nachträglich ergänzt (Update 2026-09-02) anhand Zahlungsbeleg Receipt-2842-3830.pdf.</t>
         </is>
       </c>
+      <c r="T11" s="128">
+        <f>ROUND(L11/$B$41,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="179.1" customHeight="1" s="108">
       <c r="A12" s="112" t="inlineStr">
@@ -3005,6 +3074,11 @@
           <t>Nutzungsgebühren weiter gestiegen, neu: 'Realtime Peak Connections' $10,00. Rechnung listet 5 verschiedene Projekt-Referenzen, dokumentiert sind nur 2 (Staging + Produktion). Zahlungsbeleg (Receipt-MVGOOM-00006.pdf) nachträglich ergänzt (Update 2026-09-02), keine neue Zeile.</t>
         </is>
       </c>
+      <c r="T12" s="128" t="inlineStr">
+        <is>
+          <t>0,00 (durchlaufend)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="64.90000000000001" customHeight="1" s="108">
       <c r="A13" s="112" t="inlineStr">
@@ -3089,6 +3163,10 @@
           <t>Belege für die Juni- und Juli-Abbuchung dieses Abos fehlen noch (vermutlich auch je ~22 €) — bitte in Apple-Kaufhistorie/Postfach nachsehen und ergänzen.</t>
         </is>
       </c>
+      <c r="T13" s="128">
+        <f>ROUND(L13,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="128.35" customHeight="1" s="108">
       <c r="A14" s="112" t="inlineStr">
@@ -3173,6 +3251,10 @@
           <t>Rechnung nennt eine deutsche Steuernummer (DE STN 89365407818) — da laut Sandy noch kein Gewerbe angemeldet ist (Stand 19.08.2026), vermutlich Sandys private Steuer-ID, nicht zwingend eine Geschäfts-Steuernummer. Position heißt 'Prepaid extra usage, Individual plan' — bitte klären: wiederkehrender Posten oder einmaliger Nachkauf von Nutzungsvolumen?</t>
         </is>
       </c>
+      <c r="T14" s="128">
+        <f>ROUND(L14/$B$42,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="153.7" customHeight="1" s="108">
       <c r="A15" s="112" t="inlineStr">
@@ -3257,6 +3339,10 @@
           <t>Rechnung betrifft ausschließlich die Domain 'einfach-anfrage.com' (Position 1) — das ist NICHT sofortangebot.app, sondern offensichtlich ein anderes/älteres Projekt. Deshalb Sofortangebot-Anteil = 0,00 €. Alle 5 IONOS-Rechnungen (April–August 2026) laufen unter derselben Vertragsnummer 111811442, die mehrere Domains bündelt — bitte im Blick behalten, dass hier nicht versehentlich fremde Projektkosten mitgezählt werden. Neu entdeckt und nachgetragen: Update 2026-09-02.</t>
         </is>
       </c>
+      <c r="T15" s="128">
+        <f>ROUND(L15,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="102.95" customHeight="1" s="108">
       <c r="A16" s="112" t="inlineStr">
@@ -3341,6 +3427,10 @@
           <t>Rechnung betrifft drei fremde Domains ('einfachanfrage.com', 'einfachanfrage-hochzeitsfotografie.de', 'einfachanfrage-tattoo.de') plus deren Registrierungsgebühren — keine davon ist sofortangebot.app. Deshalb Sofortangebot-Anteil = 0,00 €. Neu entdeckt und nachgetragen: Update 2026-09-02.</t>
         </is>
       </c>
+      <c r="T16" s="128">
+        <f>ROUND(L16,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="191.75" customHeight="1" s="108">
       <c r="A17" s="112" t="inlineStr">
@@ -3425,6 +3515,10 @@
           <t>Erste Rechnung mit sofortangebot.app: Domain .app registriert 08.06.2026 (12,00 € brutto). Sandy hat am 02.09.2026 bestätigt, dass 'Domain Guard' (1,00 € brutto, Privatsphärenschutz) UND 'IONOS Mail Basic 5' (2,50 €/Monat, ab 08.06.2026) ebenfalls zu sofortangebot.app gehören — damit ist die komplette Rechnung (15,50 €) dem Sofortangebot-Anteil zugeordnet. Alle 5 IONOS-Rechnungen laufen unter Vertragsnummer 111811442, die mehrere fremde Domains bündelt (siehe 2026-011/012), die weiterhin ausgeschlossen bleiben. Neu entdeckt: Update 2026-09-02, Zuordnung bestätigt 2026-09-02.</t>
         </is>
       </c>
+      <c r="T17" s="128">
+        <f>ROUND(L17,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="77.59999999999999" customHeight="1" s="108">
       <c r="A18" s="112" t="inlineStr">
@@ -3509,6 +3603,10 @@
           <t>Nur Position 'IONOS Mail Basic 5' (2,50 €) — dasselbe Postfach wie in 2026-013. Sandy hat am 02.09.2026 bestätigt, dass es zu sofortangebot.app gehört. Neu entdeckt: Update 2026-09-02, Zuordnung bestätigt 2026-09-02.</t>
         </is>
       </c>
+      <c r="T18" s="128">
+        <f>ROUND(L18,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="64.90000000000001" customHeight="1" s="108">
       <c r="A19" s="112" t="inlineStr">
@@ -3593,6 +3691,10 @@
           <t>Weiterhin 'Observability Plus' Position mit $0,00. Zahlungsart über Zahlungsbeleg bestätigt: Visa-Karte endet auf 3991 (gilt rückwirkend auch für 2026-002/005/007, dort ergänzt).</t>
         </is>
       </c>
+      <c r="T19" s="128">
+        <f>ROUND(L19/$B$42,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="179.1" customHeight="1" s="108">
       <c r="A20" s="112" t="inlineStr">
@@ -3679,6 +3781,11 @@
           <t>Nutzungsgebühren leicht gesunken ggü. Juli ($54,30 → $53,83). Positiv aufgefallen: nur noch 4 Projekt-Referenzen in den Positionen sichtbar (bkldyddstovvkkhpiqiy, ezgyklsigzaowrrpqtpv, qsdbnckgzllyypmkmzhc, yqlledouhfovytifeekd) — die fünfte aus den Vormonaten ('ytvysmwepajatcdhkgup') taucht hier nicht mehr auf. Könnte bedeuten, dass ein ungenutztes Projekt zwischenzeitlich entfernt wurde (siehe offener Punkt '5 vs. 2 dokumentierte Projekte').</t>
         </is>
       </c>
+      <c r="T20" s="128" t="inlineStr">
+        <is>
+          <t>0,00 (durchlaufend)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52.2" customHeight="1" s="108">
       <c r="A21" s="112" t="inlineStr">
@@ -3763,27 +3870,98 @@
           <t>Wie Juli: nur 'IONOS Mail Basic 5' (2,50 €). Sandy hat am 02.09.2026 bestätigt, dass es zu sofortangebot.app gehört (siehe 2026-013/014).</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="108">
-      <c r="A22" s="130" t="n"/>
-      <c r="B22" s="130" t="n"/>
-      <c r="C22" s="130" t="n"/>
-      <c r="D22" s="130" t="n"/>
-      <c r="E22" s="130" t="n"/>
-      <c r="F22" s="130" t="n"/>
-      <c r="G22" s="130" t="n"/>
-      <c r="H22" s="130" t="n"/>
-      <c r="I22" s="130" t="n"/>
-      <c r="J22" s="130" t="n"/>
-      <c r="K22" s="130" t="n"/>
-      <c r="L22" s="130" t="n"/>
-      <c r="M22" s="130" t="n"/>
-      <c r="N22" s="130" t="n"/>
-      <c r="O22" s="130" t="n"/>
-      <c r="P22" s="130" t="n"/>
-      <c r="Q22" s="130" t="n"/>
-      <c r="R22" s="130" t="n"/>
-      <c r="S22" s="130" t="n"/>
+      <c r="T21" s="128">
+        <f>ROUND(L21,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="52.2" customHeight="1" s="108">
+      <c r="A22" s="112" t="inlineStr">
+        <is>
+          <t>2026-018</t>
+        </is>
+      </c>
+      <c r="B22" s="125" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C22" s="112" t="inlineStr">
+        <is>
+          <t>B6818653</t>
+        </is>
+      </c>
+      <c r="D22" s="112" t="inlineStr">
+        <is>
+          <t>Leistung/Lieferung 04.09.2026 (Download), Bestellung 02.09.2026</t>
+        </is>
+      </c>
+      <c r="E22" s="112" t="inlineStr">
+        <is>
+          <t>DIN Media GmbH</t>
+        </is>
+      </c>
+      <c r="F22" s="112" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G22" s="112" t="inlineStr">
+        <is>
+          <t>Fachliteratur — VOB Gesamtausgabe 2019, Teil A/B/C (E-Book)</t>
+        </is>
+      </c>
+      <c r="H22" s="112" t="inlineStr">
+        <is>
+          <t>Sandra Holm, Wielandstr. 11, 12159 Berlin</t>
+        </is>
+      </c>
+      <c r="I22" s="112" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J22" s="119" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="K22" s="126" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L22" s="119" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="M22" s="119" t="n">
+        <v>54</v>
+      </c>
+      <c r="N22" s="119" t="n">
+        <v>54</v>
+      </c>
+      <c r="O22" s="112" t="inlineStr">
+        <is>
+          <t>USt. (7 % ermaessigt, § 12 Abs. 2 Nr. 14 UStG — E-Book) direkt von DIN Media ausgewiesen, USt-IdNr. DE811236989. Inlandsrechnung, kein Reverse Charge.</t>
+        </is>
+      </c>
+      <c r="P22" s="127">
+        <f>M22</f>
+        <v/>
+      </c>
+      <c r="Q22" s="112" t="inlineStr">
+        <is>
+          <t>Vorkasse, bezahlt 03.09.2026 (Auftrag 11964539), Rechnung weist 54,00 EUR als bereits gezahlt aus</t>
+        </is>
+      </c>
+      <c r="R22" s="112" t="inlineStr">
+        <is>
+          <t>406270316_ZUGFeRD.pdf</t>
+        </is>
+      </c>
+      <c r="S22" s="128" t="inlineStr">
+        <is>
+          <t>ERSTE ECHTE E-RECHNUNG IM EINGANG. ZUGFeRD/Factur-X, Profil EXTENDED, EN-16931-konform, TestIndicator=false; strukturierter Teil factur-x.xml im PDF/A-3 eingebettet. 11-Punkte-Pruefung nach § 14 UStG vollstaendig bestanden, Sicht- und XML-Teil stimmen ueberein. Einmalige Anschaffung — bewusst NICHT im Blatt Kostenuebersicht/Monatsverlauf, die nur laufende Kosten fuehren. Bestellt ueber die Privatadresse sk-holm@hotmail.de, kuenftig rechnung@sofortangebot.app verwenden.</t>
+        </is>
+      </c>
+      <c r="T22" s="128">
+        <f>ROUND(L22,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="108">
       <c r="A23" s="130" t="n"/>
@@ -3804,7 +3982,15 @@
       <c r="P23" s="130" t="n"/>
       <c r="Q23" s="130" t="n"/>
       <c r="R23" s="130" t="n"/>
-      <c r="S23" s="130" t="n"/>
+      <c r="S23" s="111" t="inlineStr">
+        <is>
+          <t>Summe erfasste Vorsteuer 2026 (Reverse Charge steht mit 0, weil durchlaufend) →</t>
+        </is>
+      </c>
+      <c r="T23" s="111">
+        <f>ROUND(SUM(T5:T22),2)</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="108">
       <c r="A24" s="218" t="n"/>
@@ -3825,7 +4011,15 @@
       <c r="P24" s="130" t="n"/>
       <c r="Q24" s="130" t="n"/>
       <c r="R24" s="130" t="n"/>
-      <c r="S24" s="130" t="n"/>
+      <c r="S24" s="111" t="inlineStr">
+        <is>
+          <t>davon STRITTIG — Abzug erst nach Klaerung (Belege 2026-001, -004, -009, -012) →</t>
+        </is>
+      </c>
+      <c r="T24" s="111">
+        <f>ROUND(T5+T8+T13+T16,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="108">
       <c r="A25" s="219" t="n"/>
@@ -3846,7 +4040,15 @@
       <c r="P25" s="130" t="n"/>
       <c r="Q25" s="130" t="n"/>
       <c r="R25" s="130" t="n"/>
-      <c r="S25" s="130" t="n"/>
+      <c r="S25" s="111" t="inlineStr">
+        <is>
+          <t>unstrittig abziehbar →</t>
+        </is>
+      </c>
+      <c r="T25" s="111">
+        <f>ROUND(T23-T24,2)</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="108">
       <c r="A26" s="130" t="n"/>
@@ -3867,7 +4069,11 @@
       <c r="P26" s="130" t="n"/>
       <c r="Q26" s="130" t="n"/>
       <c r="R26" s="130" t="n"/>
-      <c r="S26" s="130" t="n"/>
+      <c r="S26" s="130" t="inlineStr">
+        <is>
+          <t>Warum strittig — unter § 19 war das egal, unter Regelbesteuerung kostet jeder dieser Punkte den Abzug: 2026-001 und 2026-009 (Apple/Claude Pro) laufen auf "Krampasplatz 4b, 14199 Berlin", nicht auf die Betriebsanschrift Wielandstr. 11 — und die geschaeftliche Veranlassung des Abos ist ohnehin als auffaellig vermerkt. 2026-004 (OpenAI) nennt als Empfaenger "Hugo, Wielandstraße 11" — der Kontoinhaber ist geklaert, der NAME auf der Rechnung ist es nicht; § 14 Abs. 4 Nr. 1 UStG verlangt den vollstaendigen Namen des Leistungsempfaengers. 2026-012 (IONOS) betrifft ausweislich der Zeile drei fremde Domains, Sofortangebot-Anteil 0,00 € — insoweit keine betriebliche Veranlassung. Jeweils moegliche Abhilfe: berichtigte Rechnung beim Anbieter anfordern bzw. den betrieblichen Anteil belegen. Gehoert auf den Steuerberater-Termin.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="108">
       <c r="A27" s="130" t="n"/>

--- a/docs/kostenuebersicht-finance.xlsx
+++ b/docs/kostenuebersicht-finance.xlsx
@@ -4013,11 +4013,11 @@
       <c r="R24" s="130" t="n"/>
       <c r="S24" s="111" t="inlineStr">
         <is>
-          <t>davon STRITTIG — Abzug erst nach Klaerung (Belege 2026-001, -004, -009, -012) →</t>
+          <t>davon noch OFFEN — aus zwei verschiedenen Gruenden (Belege 2026-001, -009, -012) →</t>
         </is>
       </c>
       <c r="T24" s="111">
-        <f>ROUND(T5+T8+T13+T16,2)</f>
+        <f>ROUND(T5+T13+T16,2)</f>
         <v/>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       <c r="R26" s="130" t="n"/>
       <c r="S26" s="130" t="inlineStr">
         <is>
-          <t>Warum strittig — unter § 19 war das egal, unter Regelbesteuerung kostet jeder dieser Punkte den Abzug: 2026-001 und 2026-009 (Apple/Claude Pro) laufen auf "Krampasplatz 4b, 14199 Berlin", nicht auf die Betriebsanschrift Wielandstr. 11 — und die geschaeftliche Veranlassung des Abos ist ohnehin als auffaellig vermerkt. 2026-004 (OpenAI) nennt als Empfaenger "Hugo, Wielandstraße 11" — der Kontoinhaber ist geklaert, der NAME auf der Rechnung ist es nicht; § 14 Abs. 4 Nr. 1 UStG verlangt den vollstaendigen Namen des Leistungsempfaengers. 2026-012 (IONOS) betrifft ausweislich der Zeile drei fremde Domains, Sofortangebot-Anteil 0,00 € — insoweit keine betriebliche Veranlassung. Jeweils moegliche Abhilfe: berichtigte Rechnung beim Anbieter anfordern bzw. den betrieblichen Anteil belegen. Gehoert auf den Steuerberater-Termin.</t>
+          <t>KORREKTUR 17.09.2026 (Head of Finance), nach einem berechtigten Einwand von Sandy: Die erste Fassung dieser Zeilen hat 14,76 EUR als strittig gefuehrt und dabei die KLEINBETRAGSREGELUNG uebersehen. Nach § 33 UStDV braucht eine Rechnung bis 250 EUR brutto WEDER Namen NOCH Anschrift des Leistungsempfaengers — nur Lieferant, Datum, Leistung, Bruttobetrag und Steuersatz. Damit ist Beleg 2026-004 (OpenAI, "Hugo", 15,50 EUR brutto) vollstaendig abzugsfaehig, und bei den Apple-Belegen ist die abweichende Anschrift ebenfalls unschaedlich. Fast alle Belege dieses Betriebs liegen unter 250 EUR. ES BLEIBEN ZWEI ECHTE PUNKTE, beide KEINE Formfehler: (1) 2026-001 und 2026-009, Claude Pro ueber Apple, zusammen 7,02 EUR — offen ist die BETRIEBLICHE VERANLASSUNG (geschaeftlich oder privat genutzt), seit 02.09. vermerkt. (2) 2026-012, IONOS, 5,27 EUR — die Rechnung betrifft drei fremde Domains, Sofortangebot-Anteil 0,00 EUR, also insoweit keine betriebliche Veranlassung. Ausnahme von § 33 UStDV, die hier nicht greift: bei Reverse-Charge-Umsaetzen (§ 13b) gilt die Erleichterung NICHT — die Supabase-Belege brauchen weiter volle Angaben.</t>
         </is>
       </c>
     </row>

--- a/docs/kostenuebersicht-finance.xlsx
+++ b/docs/kostenuebersicht-finance.xlsx
@@ -1336,15 +1336,15 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="28" customWidth="1" style="115" min="1" max="1"/>
-    <col width="20" customWidth="1" style="115" min="2" max="2"/>
-    <col width="10" customWidth="1" style="115" min="3" max="3"/>
-    <col width="18" customWidth="1" style="115" min="4" max="4"/>
-    <col width="30" customWidth="1" style="115" min="5" max="5"/>
-    <col width="28" customWidth="1" style="115" min="6" max="6"/>
-    <col width="32" customWidth="1" style="115" min="7" max="7"/>
-    <col width="24" customWidth="1" style="115" min="8" max="8"/>
-    <col width="55" customWidth="1" style="115" min="9" max="9"/>
+    <col width="28" customWidth="1" style="213" min="1" max="1"/>
+    <col width="20" customWidth="1" style="213" min="2" max="2"/>
+    <col width="10" customWidth="1" style="213" min="3" max="3"/>
+    <col width="18" customWidth="1" style="213" min="4" max="4"/>
+    <col width="30" customWidth="1" style="213" min="5" max="5"/>
+    <col width="28" customWidth="1" style="213" min="6" max="6"/>
+    <col width="32" customWidth="1" style="213" min="7" max="7"/>
+    <col width="24" customWidth="1" style="213" min="8" max="8"/>
+    <col width="55" customWidth="1" style="213" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="116">
@@ -1976,7 +1976,7 @@
   <dimension ref="A1:A47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="100" customWidth="1" style="115" min="1" max="1"/>
+    <col width="100" customWidth="1" style="213" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="116">
@@ -2275,22 +2275,22 @@
   <dimension ref="A1:T44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="11" customWidth="1" style="115" min="1" max="1"/>
-    <col width="13" customWidth="1" style="115" min="2" max="2"/>
-    <col width="20" customWidth="1" style="115" min="3" max="3"/>
-    <col width="26" customWidth="1" style="115" min="4" max="5"/>
-    <col width="12" customWidth="1" style="115" min="6" max="6"/>
-    <col width="22" customWidth="1" style="115" min="7" max="7"/>
-    <col width="34" customWidth="1" style="115" min="8" max="8"/>
-    <col width="10" customWidth="1" style="115" min="9" max="9"/>
-    <col width="13" customWidth="1" style="115" min="10" max="11"/>
-    <col width="12" customWidth="1" style="115" min="12" max="12"/>
-    <col width="13" customWidth="1" style="115" min="13" max="13"/>
-    <col width="16" customWidth="1" style="115" min="14" max="14"/>
-    <col width="34" customWidth="1" style="115" min="15" max="15"/>
-    <col width="16" customWidth="1" style="115" min="16" max="17"/>
-    <col width="30" customWidth="1" style="115" min="18" max="18"/>
-    <col width="42" customWidth="1" style="115" min="19" max="19"/>
+    <col width="11" customWidth="1" style="213" min="1" max="1"/>
+    <col width="13" customWidth="1" style="213" min="2" max="2"/>
+    <col width="20" customWidth="1" style="213" min="3" max="3"/>
+    <col width="26" customWidth="1" style="213" min="4" max="5"/>
+    <col width="12" customWidth="1" style="213" min="6" max="6"/>
+    <col width="22" customWidth="1" style="213" min="7" max="7"/>
+    <col width="34" customWidth="1" style="213" min="8" max="8"/>
+    <col width="10" customWidth="1" style="213" min="9" max="9"/>
+    <col width="13" customWidth="1" style="213" min="10" max="11"/>
+    <col width="12" customWidth="1" style="213" min="12" max="12"/>
+    <col width="13" customWidth="1" style="213" min="13" max="13"/>
+    <col width="16" customWidth="1" style="213" min="14" max="14"/>
+    <col width="34" customWidth="1" style="213" min="15" max="15"/>
+    <col width="16" customWidth="1" style="213" min="16" max="17"/>
+    <col width="30" customWidth="1" style="213" min="18" max="18"/>
+    <col width="42" customWidth="1" style="213" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="116">
@@ -4305,7 +4305,7 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="116">
-      <c r="A39" s="115" t="inlineStr">
+      <c r="A39" s="213" t="inlineStr">
         <is>
           <t>Mai</t>
         </is>
@@ -4315,7 +4315,7 @@
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="116">
-      <c r="A40" s="115" t="inlineStr">
+      <c r="A40" s="213" t="inlineStr">
         <is>
           <t>Juni</t>
         </is>
@@ -4325,7 +4325,7 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="116">
-      <c r="A41" s="115" t="inlineStr">
+      <c r="A41" s="213" t="inlineStr">
         <is>
           <t>Juli</t>
         </is>
@@ -4335,7 +4335,7 @@
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="116">
-      <c r="A42" s="115" t="inlineStr">
+      <c r="A42" s="213" t="inlineStr">
         <is>
           <t>August</t>
         </is>
@@ -4345,7 +4345,7 @@
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="116">
-      <c r="A44" s="115" t="inlineStr">
+      <c r="A44" s="213" t="inlineStr">
         <is>
           <t>Maßgeblich ist der Monat des Rechnungsdatums (bei Supabase zugleich der Monat, in dem die Dauerleistung endet und die Steuer nach § 13b UStG entsteht). Quelle: BMF-Schreiben vom 01.09.2026, Gz. III C 3 - S 7329/00014/008/112, monatlich fortgeschriebene Übersicht 2026. Neuen Monat hier ergänzen — Spalte P rechnet dann von selbst. Für EUR-Belege verweist Spalte P unverändert auf den Bruttobetrag.</t>
         </is>
@@ -4372,9 +4372,9 @@
   <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" style="115" min="1" max="1"/>
-    <col width="13" customWidth="1" style="115" min="2" max="9"/>
-    <col width="16" customWidth="1" style="115" min="10" max="10"/>
+    <col width="30" customWidth="1" style="213" min="1" max="1"/>
+    <col width="13" customWidth="1" style="213" min="2" max="9"/>
+    <col width="16" customWidth="1" style="213" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="116">
@@ -4877,9 +4877,9 @@
   <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="60" customWidth="1" style="115" min="1" max="1"/>
-    <col width="20" customWidth="1" style="115" min="2" max="4"/>
-    <col width="18" customWidth="1" style="115" min="5" max="7"/>
+    <col width="60" customWidth="1" style="213" min="1" max="1"/>
+    <col width="20" customWidth="1" style="213" min="2" max="4"/>
+    <col width="18" customWidth="1" style="213" min="5" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="116">
@@ -5997,11 +5997,11 @@
   <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="54" customWidth="1" style="115" min="1" max="1"/>
-    <col width="14" customWidth="1" style="115" min="2" max="2"/>
-    <col width="16" customWidth="1" style="115" min="3" max="3"/>
-    <col width="20" customWidth="1" style="115" min="4" max="6"/>
-    <col width="26" customWidth="1" style="115" min="7" max="7"/>
+    <col width="54" customWidth="1" style="213" min="1" max="1"/>
+    <col width="14" customWidth="1" style="213" min="2" max="2"/>
+    <col width="16" customWidth="1" style="213" min="3" max="3"/>
+    <col width="20" customWidth="1" style="213" min="4" max="6"/>
+    <col width="26" customWidth="1" style="213" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="116">
@@ -8030,19 +8030,19 @@
   <dimension ref="A1:S93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="7" customWidth="1" style="115" min="1" max="1"/>
-    <col width="12" customWidth="1" style="115" min="2" max="2"/>
-    <col width="13" customWidth="1" style="115" min="3" max="3"/>
-    <col width="15" customWidth="1" style="115" min="4" max="4"/>
-    <col width="12" customWidth="1" style="115" min="5" max="6"/>
-    <col width="11" customWidth="1" style="115" min="7" max="7"/>
-    <col width="14" customWidth="1" style="115" min="8" max="8"/>
-    <col width="12" customWidth="1" style="115" min="9" max="11"/>
-    <col width="13" customWidth="1" style="115" min="12" max="12"/>
-    <col width="11" customWidth="1" style="115" min="13" max="13"/>
-    <col width="12" customWidth="1" style="115" min="14" max="14"/>
-    <col width="11" customWidth="1" style="115" min="15" max="16"/>
-    <col width="13" customWidth="1" style="115" min="17" max="19"/>
+    <col width="7" customWidth="1" style="213" min="1" max="1"/>
+    <col width="12" customWidth="1" style="213" min="2" max="2"/>
+    <col width="13" customWidth="1" style="213" min="3" max="3"/>
+    <col width="15" customWidth="1" style="213" min="4" max="4"/>
+    <col width="12" customWidth="1" style="213" min="5" max="6"/>
+    <col width="11" customWidth="1" style="213" min="7" max="7"/>
+    <col width="14" customWidth="1" style="213" min="8" max="8"/>
+    <col width="12" customWidth="1" style="213" min="9" max="11"/>
+    <col width="13" customWidth="1" style="213" min="12" max="12"/>
+    <col width="11" customWidth="1" style="213" min="13" max="13"/>
+    <col width="12" customWidth="1" style="213" min="14" max="14"/>
+    <col width="11" customWidth="1" style="213" min="15" max="16"/>
+    <col width="13" customWidth="1" style="213" min="17" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="116">
@@ -13953,16 +13953,16 @@
   <dimension ref="A1:AM77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="5" customWidth="1" style="115" min="1" max="2"/>
-    <col width="44" customWidth="1" style="115" min="3" max="3"/>
-    <col width="15" customWidth="1" style="115" min="4" max="4"/>
-    <col width="11" customWidth="1" style="115" min="5" max="5"/>
-    <col width="13" customWidth="1" style="115" min="6" max="6"/>
-    <col width="14" customWidth="1" style="115" min="7" max="7"/>
-    <col width="8" customWidth="1" style="115" min="8" max="8"/>
-    <col width="13" customWidth="1" style="115" min="9" max="9"/>
-    <col width="16" customWidth="1" style="115" min="10" max="13"/>
-    <col width="10" customWidth="1" style="115" min="14" max="37"/>
+    <col width="5" customWidth="1" style="213" min="1" max="2"/>
+    <col width="44" customWidth="1" style="213" min="3" max="3"/>
+    <col width="15" customWidth="1" style="213" min="4" max="4"/>
+    <col width="11" customWidth="1" style="213" min="5" max="5"/>
+    <col width="13" customWidth="1" style="213" min="6" max="6"/>
+    <col width="14" customWidth="1" style="213" min="7" max="7"/>
+    <col width="8" customWidth="1" style="213" min="8" max="8"/>
+    <col width="13" customWidth="1" style="213" min="9" max="9"/>
+    <col width="16" customWidth="1" style="213" min="10" max="13"/>
+    <col width="10" customWidth="1" style="213" min="14" max="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="116">
@@ -14107,12 +14107,12 @@
       <c r="AK6" s="147" t="n">
         <v>24</v>
       </c>
-      <c r="AL6" s="115" t="inlineStr">
+      <c r="AL6" s="213" t="inlineStr">
         <is>
           <t>Vorsteuer je € (Anteil am eingetragenen Betrag)</t>
         </is>
       </c>
-      <c r="AM6" s="115" t="inlineStr">
+      <c r="AM6" s="213" t="inlineStr">
         <is>
           <t>Basis des Betrags — warum dieser Anteil</t>
         </is>
@@ -14259,10 +14259,10 @@
         <f>IF(AK$6=$H7,$I7,0)</f>
         <v/>
       </c>
-      <c r="AL7" s="115" t="n">
+      <c r="AL7" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM7" s="115" t="inlineStr">
+      <c r="AM7" s="213" t="inlineStr">
         <is>
           <t>Behoerdengebuehr (eMeldung Berlin) — hoheitliche Leistung, keine Umsatzsteuer, keine Vorsteuer.</t>
         </is>
@@ -14338,10 +14338,10 @@
       <c r="AI8" s="139" t="n"/>
       <c r="AJ8" s="139" t="n"/>
       <c r="AK8" s="139" t="n"/>
-      <c r="AL8" s="115" t="n">
+      <c r="AL8" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM8" s="115" t="inlineStr">
+      <c r="AM8" s="213" t="inlineStr">
         <is>
           <t>UG-Block, steht nicht in der Basissumme.</t>
         </is>
@@ -14417,10 +14417,10 @@
       <c r="AI9" s="139" t="n"/>
       <c r="AJ9" s="139" t="n"/>
       <c r="AK9" s="139" t="n"/>
-      <c r="AL9" s="115" t="n">
+      <c r="AL9" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM9" s="115" t="inlineStr">
+      <c r="AM9" s="213" t="inlineStr">
         <is>
           <t>UG-Block, steht nicht in der Basissumme.</t>
         </is>
@@ -14496,10 +14496,10 @@
       <c r="AI10" s="139" t="n"/>
       <c r="AJ10" s="139" t="n"/>
       <c r="AK10" s="139" t="n"/>
-      <c r="AL10" s="115" t="n">
+      <c r="AL10" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM10" s="115" t="inlineStr">
+      <c r="AM10" s="213" t="inlineStr">
         <is>
           <t>Reserve, kein Aufwand.</t>
         </is>
@@ -14568,10 +14568,10 @@
       <c r="AI11" s="139" t="n"/>
       <c r="AJ11" s="139" t="n"/>
       <c r="AK11" s="139" t="n"/>
-      <c r="AL11" s="115" t="n">
+      <c r="AL11" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM11" s="115" t="inlineStr">
+      <c r="AM11" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -14647,10 +14647,10 @@
       <c r="AI12" s="139" t="n"/>
       <c r="AJ12" s="139" t="n"/>
       <c r="AK12" s="139" t="n"/>
-      <c r="AL12" s="115" t="n">
+      <c r="AL12" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM12" s="115" t="inlineStr">
+      <c r="AM12" s="213" t="inlineStr">
         <is>
           <t>UG-Block; Kontofuehrung ist ausserdem nach § 4 Nr. 8 UStG steuerfrei.</t>
         </is>
@@ -14719,10 +14719,10 @@
       <c r="AI13" s="139" t="n"/>
       <c r="AJ13" s="139" t="n"/>
       <c r="AK13" s="139" t="n"/>
-      <c r="AL13" s="115" t="n">
+      <c r="AL13" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM13" s="115" t="inlineStr">
+      <c r="AM13" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -14798,10 +14798,10 @@
       <c r="AI14" s="139" t="n"/>
       <c r="AJ14" s="139" t="n"/>
       <c r="AK14" s="139" t="n"/>
-      <c r="AL14" s="115" t="n">
+      <c r="AL14" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM14" s="115" t="inlineStr">
+      <c r="AM14" s="213" t="inlineStr">
         <is>
           <t>UG-Block; Kammerbeitrag ohne Umsatzsteuer.</t>
         </is>
@@ -14947,10 +14947,10 @@
         <f>IF(AK$6=$H15,$I15,0)</f>
         <v/>
       </c>
-      <c r="AL15" s="115" t="n">
+      <c r="AL15" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM15" s="115" t="inlineStr">
+      <c r="AM15" s="213" t="inlineStr">
         <is>
           <t>Honorarspanne aus B2B-Quellen = NETTO angesetzt. Unter Regelbesteuerung ist netto der richtige Planwert; ein zusaetzlicher Abzug waere doppelt gezaehlt.</t>
         </is>
@@ -15096,10 +15096,10 @@
         <f>IF(AK$6=$H16,$I16,0)</f>
         <v/>
       </c>
-      <c r="AL16" s="115" t="n">
+      <c r="AL16" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM16" s="115" t="inlineStr">
+      <c r="AM16" s="213" t="inlineStr">
         <is>
           <t>DPMA-Amtsgebuehr, keine Umsatzsteuer.</t>
         </is>
@@ -15245,11 +15245,11 @@
         <f>IF(AK$6=$H17,$I17,0)</f>
         <v/>
       </c>
-      <c r="AL17" s="115">
+      <c r="AL17" s="213">
         <f>7/107</f>
         <v/>
       </c>
-      <c r="AM17" s="115" t="inlineStr">
+      <c r="AM17" s="213" t="inlineStr">
         <is>
           <t>Fachliteratur/E-Book: 7 % (§ 12 Abs. 2 Nr. 14 UStG), Betrag brutto — gemessen an Beleg 2026-018 (DIN Media, 54,00 € brutto = 50,47 + 3,53).</t>
         </is>
@@ -15395,11 +15395,11 @@
         <f>IF(AK$6&gt;=$H18,$I18,0)</f>
         <v/>
       </c>
-      <c r="AL18" s="115">
+      <c r="AL18" s="213">
         <f>7/107</f>
         <v/>
       </c>
-      <c r="AM18" s="115" t="inlineStr">
+      <c r="AM18" s="213" t="inlineStr">
         <is>
           <t>wie Zeile darueber.</t>
         </is>
@@ -15468,10 +15468,10 @@
       <c r="AI19" s="139" t="n"/>
       <c r="AJ19" s="139" t="n"/>
       <c r="AK19" s="139" t="n"/>
-      <c r="AL19" s="115" t="n">
+      <c r="AL19" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM19" s="115" t="inlineStr">
+      <c r="AM19" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -15617,10 +15617,10 @@
         <f>IF(AK$6=$H20,$I20,0)</f>
         <v/>
       </c>
-      <c r="AL20" s="115" t="n">
+      <c r="AL20" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM20" s="115" t="inlineStr">
+      <c r="AM20" s="213" t="inlineStr">
         <is>
           <t>Reserve, kein Aufwand.</t>
         </is>
@@ -15766,10 +15766,10 @@
         <f>IF(AK$6&gt;=$H21,$I21,0)</f>
         <v/>
       </c>
-      <c r="AL21" s="115" t="n">
+      <c r="AL21" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM21" s="115" t="inlineStr">
+      <c r="AM21" s="213" t="inlineStr">
         <is>
           <t>Versicherungsbeitrag: steuerfrei nach § 4 Nr. 10 UStG (dafuer Versicherungsteuer) — keine Vorsteuer.</t>
         </is>
@@ -15915,10 +15915,10 @@
         <f>IF(AK$6&gt;=$H22,$I22,0)</f>
         <v/>
       </c>
-      <c r="AL22" s="115" t="n">
+      <c r="AL22" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM22" s="115" t="inlineStr">
+      <c r="AM22" s="213" t="inlineStr">
         <is>
           <t>Versicherungsbeitrag: steuerfrei nach § 4 Nr. 10 UStG — keine Vorsteuer.</t>
         </is>
@@ -15987,10 +15987,10 @@
       <c r="AI23" s="139" t="n"/>
       <c r="AJ23" s="139" t="n"/>
       <c r="AK23" s="139" t="n"/>
-      <c r="AL23" s="115" t="n">
+      <c r="AL23" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM23" s="115" t="inlineStr">
+      <c r="AM23" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -16137,10 +16137,10 @@
         <f>IF(AK$6&gt;=$H24,$I24,0)</f>
         <v/>
       </c>
-      <c r="AL24" s="115" t="n">
+      <c r="AL24" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM24" s="115" t="inlineStr">
+      <c r="AM24" s="213" t="inlineStr">
         <is>
           <t>Honorarspanne = NETTO angesetzt (Legal nennt 0–800 €/Jahr). Kein zusaetzlicher Abzug.</t>
         </is>
@@ -16216,10 +16216,10 @@
       <c r="AI25" s="139" t="n"/>
       <c r="AJ25" s="139" t="n"/>
       <c r="AK25" s="139" t="n"/>
-      <c r="AL25" s="115" t="n">
+      <c r="AL25" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM25" s="115" t="inlineStr">
+      <c r="AM25" s="213" t="inlineStr">
         <is>
           <t>UG-Block.</t>
         </is>
@@ -16366,11 +16366,11 @@
         <f>IF(AK$6&gt;=$H26,$I26,0)</f>
         <v/>
       </c>
-      <c r="AL26" s="115">
+      <c r="AL26" s="213">
         <f>19/119</f>
         <v/>
       </c>
-      <c r="AM26" s="115" t="inlineStr">
+      <c r="AM26" s="213" t="inlineStr">
         <is>
           <t>Betrag ausdruecklich brutto (11,90 € netto = 14,16 € brutto, Quellenzeile daneben).</t>
         </is>
@@ -16440,10 +16440,10 @@
       <c r="AI27" s="139" t="n"/>
       <c r="AJ27" s="139" t="n"/>
       <c r="AK27" s="139" t="n"/>
-      <c r="AL27" s="115" t="n">
+      <c r="AL27" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM27" s="115" t="inlineStr">
+      <c r="AM27" s="213" t="inlineStr">
         <is>
           <t>Einkommensteuer, keine Vorsteuer.</t>
         </is>
@@ -16512,10 +16512,10 @@
       <c r="AI28" s="139" t="n"/>
       <c r="AJ28" s="139" t="n"/>
       <c r="AK28" s="139" t="n"/>
-      <c r="AL28" s="115" t="n">
+      <c r="AL28" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM28" s="115" t="inlineStr">
+      <c r="AM28" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -16584,10 +16584,10 @@
       <c r="AI29" s="139" t="n"/>
       <c r="AJ29" s="139" t="n"/>
       <c r="AK29" s="139" t="n"/>
-      <c r="AL29" s="115" t="n">
+      <c r="AL29" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM29" s="115" t="inlineStr">
+      <c r="AM29" s="213" t="inlineStr">
         <is>
           <t>nicht simuliert.</t>
         </is>
@@ -16656,10 +16656,10 @@
       <c r="AI30" s="139" t="n"/>
       <c r="AJ30" s="139" t="n"/>
       <c r="AK30" s="139" t="n"/>
-      <c r="AL30" s="115" t="n">
+      <c r="AL30" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM30" s="115" t="inlineStr">
+      <c r="AM30" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -16729,10 +16729,10 @@
       <c r="AI31" s="139" t="n"/>
       <c r="AJ31" s="139" t="n"/>
       <c r="AK31" s="139" t="n"/>
-      <c r="AL31" s="115" t="n">
+      <c r="AL31" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM31" s="115" t="inlineStr">
+      <c r="AM31" s="213" t="inlineStr">
         <is>
           <t>Schalterzeile, kein Betrag.</t>
         </is>
@@ -16801,10 +16801,10 @@
       <c r="AI32" s="139" t="n"/>
       <c r="AJ32" s="139" t="n"/>
       <c r="AK32" s="139" t="n"/>
-      <c r="AL32" s="115" t="n">
+      <c r="AL32" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM32" s="115" t="inlineStr">
+      <c r="AM32" s="213" t="inlineStr">
         <is>
           <t>Ergebniszeile, wird unten gerechnet.</t>
         </is>
@@ -16950,10 +16950,10 @@
         <f>IF(AK$6&gt;=$H33,$I33,0)</f>
         <v/>
       </c>
-      <c r="AL33" s="115" t="n">
+      <c r="AL33" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM33" s="115" t="inlineStr">
+      <c r="AM33" s="213" t="inlineStr">
         <is>
           <t>Reverse Charge § 13b UStG: Supabase weist keine USt aus. Unter Regelbesteuerung angemeldet und im selben Zug gezogen — durchlaufend, Saldo null.</t>
         </is>
@@ -17099,11 +17099,11 @@
         <f>IF(AK$6&gt;=$H34,$I34,0)</f>
         <v/>
       </c>
-      <c r="AL34" s="115">
+      <c r="AL34" s="213">
         <f>19/119</f>
         <v/>
       </c>
-      <c r="AM34" s="115" t="inlineStr">
+      <c r="AM34" s="213" t="inlineStr">
         <is>
           <t>Beleg brutto inkl. 19 % (Journal 2026-002/005/007/015, EU VAT EU056329113) — Vercel rechnet KEIN Reverse Charge ab.</t>
         </is>
@@ -17249,11 +17249,11 @@
         <f>IF(AK$6&gt;=$H35,$I35,0)</f>
         <v/>
       </c>
-      <c r="AL35" s="115">
+      <c r="AL35" s="213">
         <f>19/119</f>
         <v/>
       </c>
-      <c r="AM35" s="115" t="inlineStr">
+      <c r="AM35" s="213" t="inlineStr">
         <is>
           <t>Beleg brutto inkl. 19 % (Journal 2026-010, EU VAT IE4276970QH).</t>
         </is>
@@ -17399,11 +17399,11 @@
         <f>IF(AK$6&gt;=$H36,$I36,0)</f>
         <v/>
       </c>
-      <c r="AL36" s="115">
+      <c r="AL36" s="213">
         <f>19/119</f>
         <v/>
       </c>
-      <c r="AM36" s="115" t="inlineStr">
+      <c r="AM36" s="213" t="inlineStr">
         <is>
           <t>Beleg brutto inkl. 19 % (Journal 2026-001/009, Apple Distribution International).</t>
         </is>
@@ -17550,11 +17550,11 @@
         <f>IF(AK$6&gt;=$H37,$I37,0)</f>
         <v/>
       </c>
-      <c r="AL37" s="115">
+      <c r="AL37" s="213">
         <f>19/119</f>
         <v/>
       </c>
-      <c r="AM37" s="115" t="inlineStr">
+      <c r="AM37" s="213" t="inlineStr">
         <is>
           <t>Beleg brutto inkl. 19 % (Journal 2026-011 bis -017, IONOS SE, USt-IdNr. DE815563912).</t>
         </is>
@@ -17700,10 +17700,10 @@
         <f>IF(AK$6&gt;=$H38,$I38,0)</f>
         <v/>
       </c>
-      <c r="AL38" s="115" t="n">
+      <c r="AL38" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM38" s="115" t="inlineStr">
+      <c r="AM38" s="213" t="inlineStr">
         <is>
           <t>Betrag 0.</t>
         </is>
@@ -17772,10 +17772,10 @@
       <c r="AI39" s="139" t="n"/>
       <c r="AJ39" s="139" t="n"/>
       <c r="AK39" s="139" t="n"/>
-      <c r="AL39" s="115" t="n">
+      <c r="AL39" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM39" s="115" t="inlineStr">
+      <c r="AM39" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -17845,10 +17845,10 @@
       <c r="AI40" s="139" t="n"/>
       <c r="AJ40" s="139" t="n"/>
       <c r="AK40" s="139" t="n"/>
-      <c r="AL40" s="115" t="n">
+      <c r="AL40" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM40" s="115" t="inlineStr">
+      <c r="AM40" s="213" t="inlineStr">
         <is>
           <t>variabel, laeuft im Raster ueber Plan-24M Spalte K (unveraendert). Die 2,5 Cent sind ein Netto-Listenpreis in USD — unter Regelbesteuerung damit bereits der richtige Kostenwert.</t>
         </is>
@@ -17918,10 +17918,10 @@
       <c r="AI41" s="139" t="n"/>
       <c r="AJ41" s="139" t="n"/>
       <c r="AK41" s="139" t="n"/>
-      <c r="AL41" s="115" t="n">
+      <c r="AL41" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM41" s="115" t="inlineStr">
+      <c r="AM41" s="213" t="inlineStr">
         <is>
           <t>Zahlungsdienstleistung, steuerfrei nach § 4 Nr. 8 UStG — keine Vorsteuer.</t>
         </is>
@@ -17990,10 +17990,10 @@
       <c r="AI42" s="139" t="n"/>
       <c r="AJ42" s="139" t="n"/>
       <c r="AK42" s="139" t="n"/>
-      <c r="AL42" s="115" t="n">
+      <c r="AL42" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM42" s="115" t="inlineStr">
+      <c r="AM42" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -18139,10 +18139,10 @@
         <f>IF(AK$6&gt;=$H43,$I43,0)</f>
         <v/>
       </c>
-      <c r="AL43" s="115" t="n">
+      <c r="AL43" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM43" s="115" t="inlineStr">
+      <c r="AM43" s="213" t="inlineStr">
         <is>
           <t>als NETTO angesetzt, bis der erste Beleg vorliegt: Apple stellt Entwicklern mit USt-IdNr. ohne deutsche USt. Sobald ein Beleg mit USt-Ausweis da ist, hier 19/119 eintragen.</t>
         </is>
@@ -18288,10 +18288,10 @@
         <f>IF(AK$6=$H44,$I44,0)</f>
         <v/>
       </c>
-      <c r="AL44" s="115" t="n">
+      <c r="AL44" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM44" s="115" t="inlineStr">
+      <c r="AM44" s="213" t="inlineStr">
         <is>
           <t>als NETTO angesetzt, bis der erste Beleg vorliegt — wie Apple Developer.</t>
         </is>
@@ -18437,11 +18437,11 @@
         <f>IF(AK$6&gt;=$H45,$I45,0)</f>
         <v/>
       </c>
-      <c r="AL45" s="115">
+      <c r="AL45" s="213">
         <f>19/119</f>
         <v/>
       </c>
-      <c r="AM45" s="115" t="inlineStr">
+      <c r="AM45" s="213" t="inlineStr">
         <is>
           <t>Platzhalter fuer zusaetzliche Anthropic-Kosten — wie Zeile 29 brutto inkl. 19 %.</t>
         </is>
@@ -18510,10 +18510,10 @@
       <c r="AI46" s="139" t="n"/>
       <c r="AJ46" s="139" t="n"/>
       <c r="AK46" s="139" t="n"/>
-      <c r="AL46" s="115" t="n">
+      <c r="AL46" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM46" s="115" t="inlineStr">
+      <c r="AM46" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -18539,7 +18539,7 @@
         </is>
       </c>
       <c r="E47" s="181" t="n">
-        <v>1430</v>
+        <v>1350</v>
       </c>
       <c r="F47" s="149" t="inlineStr">
         <is>
@@ -18555,14 +18555,14 @@
       <c r="I47" s="139" t="n"/>
       <c r="J47" s="157" t="inlineStr">
         <is>
-          <t>Zulieferung Marketing (gtm-kanalplan.xlsx, 'Sachkosten — gesamt'): Oktober 260 € (Flyer, Aufsteller, Anstecker), dann 10–20 €/Monat, ab April 2027 je 100 € pro kaltem Fachhandel-Laden. Summe 1.430 €. Werte je Monat rechts — Größenordnungen, keine Angebote. Alle Betraege BRUTTO (von Marketing am 23.09.2026 bestaetigt) — Vorsteuer siehe Spalte AL/AM.</t>
+          <t>Zulieferung Marketing (gtm-kanalplan.xlsx, 'Sachkosten — gesamt'): Oktober 180 € (Flyer, Aufsteller, Ansteckmikro/Stativ), dann 10–20 €/Monat, ab April 2027 je 100 € pro kaltem Fachhandel-Laden. Summe 1.350 €. Werte je Monat rechts — Größenordnungen, keine Angebote. Alle Beträge BRUTTO (von Marketing am 23.09.2026 bestätigt) — Vorsteuer siehe Spalte AL/AM. GEÄNDERT am 23.09.2026: die zwei Dessau-Fahrten im Oktober 2026 (vorher 80 €) stehen auf 0 €, weil Sandys Deutschlandticket sie abdeckt — die Summe sinkt von 1.430 € auf 1.350 €.</t>
         </is>
       </c>
       <c r="N47" s="212" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="212" t="n">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="P47" s="212" t="n">
         <v>0</v>
@@ -18630,13 +18630,13 @@
       <c r="AK47" s="212" t="n">
         <v>110</v>
       </c>
-      <c r="AL47" s="115">
-        <f>(660*19/119+440*7/107+60*19/119+270*19/119)/1430</f>
+      <c r="AL47" s="213">
+        <f>(660*19/119+360*7/107+60*19/119+270*19/119)/1350</f>
         <v/>
       </c>
       <c r="AM47" s="213" t="inlineStr">
         <is>
-          <t>Groessenordnungen von Marketing (gtm-kanalplan.xlsx, Blatt „Annahmen"), am 23.09.2026 von Marketing ausdruecklich als BRUTTO bestaetigt (Endpreise inkl. USt) — ERSETZT den Ansatz „netto, Vorsteuer 0" vom 21.09.2026. Zusammensetzung der 1.430 EUR und Steuersaetze: Druck Flyer/Aufsteller 660 EUR zu 19 % = 105,38 EUR - Fahrten 440 EUR zu 7 % = 28,79 EUR (Bahn RE7 Berlin&lt;&gt;Dessau ohne Umsteigen, ca. 20 EUR je Richtung; Personenbefoerderung im Schienenbahnverkehr, § 12 Abs. 2 Nr. 10 UStG, ermaessigt seit 01.01.2020) - Ausruestung Ansteckmikro/Stativ 60 EUR zu 19 % = 9,58 EUR - laufender Kleinbedarf 270 EUR zu 19 % = 43,11 EUR. Summe Vorsteuer ueber 24 Monate 186,85 EUR, Anteil am Betrag 0,1306659. Die Zelle traegt bewusst einen Mischsatz, weil die Zeile ein Monatsvektor mit wechselnder Zusammensetzung ist: ueber die 24 Monate stimmt die Vorsteuer auf den Cent, die groesste Abweichung in einem einzelnen Monat betraegt 0,58 EUR (nachgerechnet Monat fuer Monat am 23.09.2026). Quelle der Steuersaetze und der Brutto-Aussage: Antwort Head of Marketing, 23.09.2026, 07:20 UTC, docs/chief-of-staff-finance-todos.md; die Annahmen stehen seit dem 23.09.2026 auch im Kanalplan selbst (Felder F2, F4, F6, A13). ZWEI VORBEHALTE: (1) Die 270 EUR Kleinbedarf sind nicht aufgeschluesselt; Kleinkram ohne Rechnung mit ausgewiesener Steuer senkt die 43,11 EUR, schlimmstenfalls auf 0. (2) Faehrt Sandy mit dem Pkw statt mit der Bahn, steigt die Fahrtzeile von 440 EUR auf rund 860 EUR (0,30 EUR/km Kilometerpauschale, ca. 260 km hin und zurueck je Fahrt) und traegt 0 EUR Vorsteuer — das sind rund 420 EUR Mehrkosten, nicht nur eine andere Vorsteuer. Frage an Sandy gestellt am 23.09.2026 (docs/entscheidungen-fuer-sandy.md).</t>
+          <t>Groessenordnungen von Marketing (gtm-kanalplan.xlsx, Blatt „Annahmen"), am 23.09.2026 von Marketing ausdruecklich als BRUTTO bestaetigt (Endpreise inkl. USt). STAND 23.09.2026, 10:00 UTC — ERSETZT die Fassung von 07:00 UTC (1.430 EUR / 186,85 EUR), weil Sandy die Fahrtfrage beantwortet hat. Zusammensetzung der 1.350 EUR und Steuersaetze: Druck Flyer/Aufsteller 660 EUR zu 19 % = 105,38 EUR - Fahrten 360 EUR zu 7 % = 23,55 EUR - Ausruestung Ansteckmikro/Stativ 60 EUR zu 19 % = 9,58 EUR - laufender Kleinbedarf 270 EUR zu 19 % = 43,11 EUR. Summe Vorsteuer ueber 24 Monate 181,62 EUR, Anteil am Betrag 0,1345323176. FAHRTEN — zwei verschiedene Faelle, bewusst unterschiedlich behandelt: (a) Die zwei Dessau-Fahrten im Oktober 2026 (frueher 2 x 40 EUR = 80 EUR) stehen auf 0 EUR. Sandy faehrt mit dem Deutschlandticket, das sie fuer ihren Angestelltenjob ohnehin haelt und privat bezahlt (Sandys Antwort, 23.09.2026). Eine privat gehaltene Monatskarte, die ohne den Betrieb genauso gekauft wuerde, verursacht keine zusaetzliche Betriebsausgabe; es gibt keine auf den Betrieb lautende Rechnung und damit auch keinen Vorsteuerabzug nach § 15 Abs. 1 UStG. Deshalb 0 EUR Kosten UND 0 EUR Vorsteuer, nicht 80 EUR zu 7 %. (b) Die 9 Fahrten zu kalten Fachhandel-Laeden ab April 2027 (9 x 40 EUR = 360 EUR) bleiben mit 7 % stehen. Begruendung: das Ticket haengt an Sandys Angestelltenjob, dieser Kanal startet erst in 19 Monaten, und welche Laeden es werden, steht nicht fest. Das ist der vorsichtige Ansatz - faellt das Ticket dort ebenfalls an, wird der Plan um bis zu 360 EUR billiger, nicht teurer. UEBERNACHTUNG: keine eigene Zeile, und das ist eine Entscheidung. Dessau ist von Berlin mit dem RE7 ohne Umsteigen in rund zwei Stunden je Richtung erreichbar; alle Besuche sind als Tagesfahrten geplant (Marketing, gtm-kanalplan.xlsx Feld F2). Sandy hat am 23.09.2026 zusaetzlich gesagt, sie koenne „ggfs" kostenlos bei Clemens uebernachten - das ist eine Moeglichkeit, keine Zusage, und der Plan stuetzt sich nicht darauf. Groessenordnung, falls doch: eine Uebernachtung in Dessau kostet 60-90 EUR brutto (7 % auf die Beherbergung, § 12 Abs. 2 Nr. 11 UStG, 19 % auf Fruehstueck). Ab etwa vier Uebernachtungen in den 24 Monaten waere eine eigene Zeile faellig; darunter geht es im Kleinbedarf unter. MISCHSATZ: Die Zelle traegt bewusst einen Mischsatz, weil die Spalte genau einen Faktor je Zeile erlaubt, die Zeile aber ein Monatsvektor mit wechselnder Zusammensetzung ist. Ueber die 24 Monate stimmt die Vorsteuer auf den Cent (181,6186 EUR exakt wie gemischt). Die groesste Abweichung in einem einzelnen Monat ist jetzt 4,52 EUR und liegt im Oktober 2026 (exakt 28,74 EUR, gemischt 24,22 EUR) - vorher waren es 0,58 EUR. Der Sprung kommt daher, dass der Oktober nach dem Wegfall der Bahnfahrten nur noch 19-%-Posten enthaelt, der Mischsatz aber die 7 % der spaeteren Fahrten mittraegt. Eine eigene Zeile fuer die Fahrten wuerde das auf null bringen, verschoebe aber die Zeilennummern, an denen $AL$7:$AL$55 und die Raster haengen; 4,52 EUR in einem einzigen Monat rechtfertigen dieses Risiko nicht. In allen uebrigen Monaten liegt die Abweichung unter 1,01 EUR. VORBEHALT: Die 270 EUR Kleinbedarf sind nicht aufgeschluesselt; Kleinkram ohne Rechnung mit ausgewiesener Steuer senkt die 43,11 EUR, schlimmstenfalls auf 0. Loest der erste echte Beleg, nicht eine weitere Frage. Quellen: Antwort Head of Marketing 23.09.2026 07:20 UTC und Kanalplan-Stand 09:52 UTC (Felder F2, F4, F6, A13, A14) - Sandys Antwort zur Fahrtfrage, weitergegeben vom Chief of Staff, 23.09.2026 08:10 UTC, docs/chief-of-staff-finance-todos.md - § 12 Abs. 2 Nr. 10 UStG (Schienen-Nahverkehr 7 %) - § 15 Abs. 1 UStG (Vorsteuerabzug setzt Leistungsbezug fuer das Unternehmen voraus).</t>
         </is>
       </c>
     </row>
@@ -18703,10 +18703,10 @@
       <c r="AI48" s="139" t="n"/>
       <c r="AJ48" s="139" t="n"/>
       <c r="AK48" s="139" t="n"/>
-      <c r="AL48" s="115" t="n">
+      <c r="AL48" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM48" s="115" t="inlineStr">
+      <c r="AM48" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -18776,10 +18776,10 @@
       <c r="AI49" s="139" t="n"/>
       <c r="AJ49" s="139" t="n"/>
       <c r="AK49" s="139" t="n"/>
-      <c r="AL49" s="115" t="n">
+      <c r="AL49" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM49" s="115" t="inlineStr">
+      <c r="AM49" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -18848,10 +18848,10 @@
       <c r="AI50" s="139" t="n"/>
       <c r="AJ50" s="139" t="n"/>
       <c r="AK50" s="139" t="n"/>
-      <c r="AL50" s="115" t="n">
+      <c r="AL50" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM50" s="115" t="inlineStr">
+      <c r="AM50" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -18921,10 +18921,10 @@
       <c r="AI51" s="139" t="n"/>
       <c r="AJ51" s="139" t="n"/>
       <c r="AK51" s="139" t="n"/>
-      <c r="AL51" s="115" t="n">
+      <c r="AL51" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM51" s="115" t="inlineStr">
+      <c r="AM51" s="213" t="inlineStr">
         <is>
           <t>Erloesminderung, keine Vorsteuer.</t>
         </is>
@@ -18994,10 +18994,10 @@
       <c r="AI52" s="139" t="n"/>
       <c r="AJ52" s="139" t="n"/>
       <c r="AK52" s="139" t="n"/>
-      <c r="AL52" s="115" t="n">
+      <c r="AL52" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM52" s="115" t="inlineStr">
+      <c r="AM52" s="213" t="inlineStr">
         <is>
           <t>Erloesminderung, keine Vorsteuer.</t>
         </is>
@@ -19067,10 +19067,10 @@
       <c r="AI53" s="139" t="n"/>
       <c r="AJ53" s="139" t="n"/>
       <c r="AK53" s="139" t="n"/>
-      <c r="AL53" s="115" t="n">
+      <c r="AL53" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM53" s="115" t="inlineStr">
+      <c r="AM53" s="213" t="inlineStr">
         <is>
           <t>Preiszeile, kein Kostenbetrag.</t>
         </is>
@@ -19140,10 +19140,10 @@
       <c r="AI54" s="139" t="n"/>
       <c r="AJ54" s="139" t="n"/>
       <c r="AK54" s="139" t="n"/>
-      <c r="AL54" s="115" t="n">
+      <c r="AL54" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM54" s="115" t="inlineStr">
+      <c r="AM54" s="213" t="inlineStr">
         <is>
           <t>Schalterzeile, kein Betrag.</t>
         </is>
@@ -19212,10 +19212,10 @@
       <c r="AI55" s="139" t="n"/>
       <c r="AJ55" s="139" t="n"/>
       <c r="AK55" s="139" t="n"/>
-      <c r="AL55" s="115" t="n">
+      <c r="AL55" s="213" t="n">
         <v>0</v>
       </c>
-      <c r="AM55" s="115" t="inlineStr">
+      <c r="AM55" s="213" t="inlineStr">
         <is>
           <t>trifft nicht zu.</t>
         </is>
@@ -20049,27 +20049,27 @@
   <dimension ref="A1:AE90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="7" customWidth="1" style="115" min="1" max="1"/>
-    <col width="12" customWidth="1" style="115" min="2" max="2"/>
-    <col width="10" customWidth="1" style="115" min="3" max="7"/>
-    <col width="12" customWidth="1" style="115" min="8" max="8"/>
-    <col width="11" customWidth="1" style="115" min="9" max="10"/>
-    <col width="10" customWidth="1" style="115" min="11" max="11"/>
-    <col width="12" customWidth="1" style="115" min="12" max="12"/>
-    <col width="13" customWidth="1" style="115" min="13" max="14"/>
-    <col width="12" customWidth="1" style="115" min="15" max="17"/>
-    <col width="13" customWidth="1" style="115" min="18" max="18"/>
-    <col width="11" customWidth="1" style="115" min="19" max="19"/>
-    <col width="12" customWidth="1" style="115" min="20" max="21"/>
-    <col width="11" customWidth="1" style="115" min="22" max="22"/>
-    <col width="12" customWidth="1" style="115" min="23" max="23"/>
-    <col width="9" customWidth="1" style="115" min="24" max="24"/>
-    <col width="10" customWidth="1" style="115" min="25" max="25"/>
-    <col width="11" customWidth="1" style="115" min="26" max="26"/>
-    <col width="12" customWidth="1" style="115" min="27" max="28"/>
-    <col width="10" customWidth="1" style="115" min="29" max="29"/>
-    <col width="13" customWidth="1" style="115" min="30" max="30"/>
-    <col width="9" customWidth="1" style="115" min="31" max="31"/>
+    <col width="7" customWidth="1" style="213" min="1" max="1"/>
+    <col width="12" customWidth="1" style="213" min="2" max="2"/>
+    <col width="10" customWidth="1" style="213" min="3" max="7"/>
+    <col width="12" customWidth="1" style="213" min="8" max="8"/>
+    <col width="11" customWidth="1" style="213" min="9" max="10"/>
+    <col width="10" customWidth="1" style="213" min="11" max="11"/>
+    <col width="12" customWidth="1" style="213" min="12" max="12"/>
+    <col width="13" customWidth="1" style="213" min="13" max="14"/>
+    <col width="12" customWidth="1" style="213" min="15" max="17"/>
+    <col width="13" customWidth="1" style="213" min="18" max="18"/>
+    <col width="11" customWidth="1" style="213" min="19" max="19"/>
+    <col width="12" customWidth="1" style="213" min="20" max="21"/>
+    <col width="11" customWidth="1" style="213" min="22" max="22"/>
+    <col width="12" customWidth="1" style="213" min="23" max="23"/>
+    <col width="9" customWidth="1" style="213" min="24" max="24"/>
+    <col width="10" customWidth="1" style="213" min="25" max="25"/>
+    <col width="11" customWidth="1" style="213" min="26" max="26"/>
+    <col width="12" customWidth="1" style="213" min="27" max="28"/>
+    <col width="10" customWidth="1" style="213" min="29" max="29"/>
+    <col width="13" customWidth="1" style="213" min="30" max="30"/>
+    <col width="9" customWidth="1" style="213" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="116">
@@ -29881,9 +29881,9 @@
   <dimension ref="A1:I187"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="56" customWidth="1" style="115" min="1" max="1"/>
-    <col width="17" customWidth="1" style="115" min="2" max="5"/>
-    <col width="15" customWidth="1" style="115" min="6" max="9"/>
+    <col width="56" customWidth="1" style="213" min="1" max="1"/>
+    <col width="17" customWidth="1" style="213" min="2" max="5"/>
+    <col width="15" customWidth="1" style="213" min="6" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="116">
